--- a/data/trans_dic/P21B_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P21B_R-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>94,28%</t>
         </is>
       </c>
     </row>
@@ -717,27 +717,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>87,16; 100,0</t>
+          <t>87,28; 100,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>91,47; 99,06</t>
+          <t>91,7; 99,05</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>86,0; 98,71</t>
+          <t>85,67; 98,03</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>85,0; 97,25</t>
+          <t>87,59; 96,94</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>86,8; 100,0</t>
+          <t>87,1; 100,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -747,32 +747,32 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,35; 99,12</t>
+          <t>89,88; 99,11</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>90,47; 97,54</t>
+          <t>90,77; 97,25</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>91,13; 99,02</t>
+          <t>91,12; 99,01</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>95,89; 99,54</t>
+          <t>95,79; 99,54</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>91,2; 98,23</t>
+          <t>90,54; 97,97</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>89,87; 96,41</t>
+          <t>91,07; 96,48</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,65%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>88,17; 100,0</t>
+          <t>87,92; 100,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>94,11; 99,29</t>
+          <t>94,25; 99,3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>85,65; 98,73</t>
+          <t>85,36; 98,73</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>85,28; 98,5</t>
+          <t>85,27; 98,36</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>95,41; 100,0</t>
+          <t>95,21; 100,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>93,21; 99,01</t>
+          <t>92,19; 99,01</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>89,84; 98,22</t>
+          <t>90,06; 98,21</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>90,42; 97,94</t>
+          <t>90,49; 98,12</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>94,02; 99,49</t>
+          <t>93,34; 99,14</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>94,76; 98,82</t>
+          <t>94,71; 98,81</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>90,28; 97,82</t>
+          <t>90,6; 97,41</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>90,64; 97,11</t>
+          <t>90,05; 97,29</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>95,18%</t>
         </is>
       </c>
     </row>
@@ -997,22 +997,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>86,97; 98,7</t>
+          <t>85,94; 98,5</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>90,92; 100,0</t>
+          <t>91,14; 100,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>81,03; 97,59</t>
+          <t>81,53; 97,6</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>83,3; 96,72</t>
+          <t>86,45; 96,88</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1022,37 +1022,37 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>90,03; 100,0</t>
+          <t>89,55; 100,0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>79,51; 96,37</t>
+          <t>78,25; 96,09</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>90,8; 98,98</t>
+          <t>91,9; 98,99</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>94,37; 99,41</t>
+          <t>94,42; 99,41</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>93,03; 99,42</t>
+          <t>93,44; 99,42</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>83,8; 95,76</t>
+          <t>84,18; 95,79</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>91,14; 97,54</t>
+          <t>91,96; 97,52</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>92,29%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>91,24; 100,0</t>
+          <t>91,62; 100,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>87,17; 100,0</t>
+          <t>85,83; 100,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>87,7; 98,35</t>
+          <t>88,52; 98,94</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>74,85; 98,41</t>
+          <t>77,79; 98,65</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>91,93; 99,08</t>
+          <t>91,91; 99,09</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,66; 99,02</t>
+          <t>91,38; 99,05</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>82,25; 94,71</t>
+          <t>82,48; 95,16</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>84,63; 95,49</t>
+          <t>85,42; 95,95</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>93,79; 98,95</t>
+          <t>93,72; 98,93</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>92,29; 98,55</t>
+          <t>91,31; 98,39</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>87,98; 95,71</t>
+          <t>87,86; 95,58</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>84,45; 95,76</t>
+          <t>85,16; 96,02</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>92,05%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>94,98%</t>
         </is>
       </c>
     </row>
@@ -1277,32 +1277,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>87,21; 100,0</t>
+          <t>86,96; 100,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>80,47; 100,0</t>
+          <t>83,15; 100,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>77,9; 100,0</t>
+          <t>77,95; 100,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>73,74; 100,0</t>
+          <t>73,19; 100,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>84,82; 100,0</t>
+          <t>84,66; 100,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>91,56; 100,0</t>
+          <t>91,57; 100,0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1317,22 +1317,22 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>89,03; 100,0</t>
+          <t>88,92; 100,0</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>91,58; 99,15</t>
+          <t>91,64; 99,12</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>89,29; 100,0</t>
+          <t>89,63; 100,0</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>84,17; 100,0</t>
+          <t>83,55; 100,0</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,25%</t>
         </is>
       </c>
     </row>
@@ -1427,22 +1427,22 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>91,48; 100,0</t>
+          <t>89,95; 100,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>92,19; 99,34</t>
+          <t>91,33; 99,36</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>93,13; 100,0</t>
+          <t>93,55; 100,0</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>94,54; 100,0</t>
+          <t>94,98; 100,0</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1452,27 +1452,27 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>92,75; 99,3</t>
+          <t>92,28; 99,35</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>95,95; 100,0</t>
+          <t>96,26; 100,0</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>96,97; 100,0</t>
+          <t>96,99; 100,0</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>95,81; 100,0</t>
+          <t>95,53; 100,0</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>94,49; 98,9</t>
+          <t>94,09; 98,79</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>85,74%</t>
+          <t>85,65%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>85,58%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>85,61%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>82,66; 95,15</t>
+          <t>83,15; 94,94</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>96,16; 100,0</t>
+          <t>95,63; 100,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>83,99; 97,07</t>
+          <t>83,46; 96,98</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>78,81; 90,06</t>
+          <t>79,72; 90,48</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>87,87; 96,37</t>
+          <t>87,72; 96,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,48; 98,42</t>
+          <t>92,38; 98,38</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>80,71; 93,59</t>
+          <t>82,42; 94,28</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>83,55; 98,14</t>
+          <t>81,52; 89,19</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>87,97; 94,66</t>
+          <t>87,79; 95,02</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>95,08; 98,59</t>
+          <t>95,01; 98,77</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>85,1; 94,18</t>
+          <t>84,8; 93,61</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>84,2; 96,36</t>
+          <t>81,84; 88,64</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>89,46%</t>
+          <t>89,74%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>90,08%</t>
+          <t>90,34%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>88,97; 98,9</t>
+          <t>89,14; 98,9</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>88,42; 98,64</t>
+          <t>88,06; 98,67</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>76,82; 91,88</t>
+          <t>75,16; 90,84</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>84,59; 95,97</t>
+          <t>82,76; 95,53</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>93,0; 98,9</t>
+          <t>93,22; 99,03</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>85,12; 96,98</t>
+          <t>84,69; 96,4</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>81,75; 93,42</t>
+          <t>81,16; 93,08</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>83,02; 93,56</t>
+          <t>83,23; 94,6</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>93,43; 98,27</t>
+          <t>93,32; 98,38</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>88,61; 96,62</t>
+          <t>88,31; 96,57</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>82,0; 91,06</t>
+          <t>81,95; 91,41</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>85,57; 93,62</t>
+          <t>85,71; 93,47</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>91,53%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>93,33; 96,91</t>
+          <t>93,1; 96,98</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>95,88; 98,46</t>
+          <t>95,99; 98,57</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>90,09; 94,58</t>
+          <t>90,25; 94,67</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>88,66; 93,49</t>
+          <t>88,48; 93,29</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>95,29; 97,81</t>
+          <t>95,36; 97,81</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>95,58; 97,89</t>
+          <t>95,44; 97,91</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>90,33; 94,61</t>
+          <t>90,08; 94,52</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>90,89; 96,5</t>
+          <t>89,83; 93,19</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>95,04; 97,16</t>
+          <t>95,08; 97,2</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>96,08; 97,81</t>
+          <t>96,06; 97,84</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>91,07; 94,09</t>
+          <t>91,18; 94,18</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>90,95; 95,08</t>
+          <t>89,96; 92,83</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>99875</t>
+          <t>99267</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>107256</t>
+          <t>115560</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>207132</t>
+          <t>214826</t>
         </is>
       </c>
     </row>
@@ -2209,27 +2209,27 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>33609; 38562</t>
+          <t>33656; 38562</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>92394; 100056</t>
+          <t>92622; 100051</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>71984; 82618</t>
+          <t>71704; 82050</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>90915; 104021</t>
+          <t>92922; 102846</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>48689; 56095</t>
+          <t>48859; 56095</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -2239,32 +2239,32 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>94070; 103202</t>
+          <t>93578; 103188</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>102661; 110684</t>
+          <t>110528; 118415</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>86265; 93734</t>
+          <t>86253; 93724</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>203060; 210799</t>
+          <t>202848; 210801</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>171299; 184485</t>
+          <t>170053; 184008</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>198101; 212518</t>
+          <t>207503; 219826</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>73967</t>
+          <t>76080</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>97953</t>
+          <t>102978</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>171920</t>
+          <t>179058</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>66545; 75472</t>
+          <t>66358; 75472</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>123574; 130377</t>
+          <t>123758; 130382</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>70731; 81535</t>
+          <t>70495; 81535</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>67049; 77444</t>
+          <t>69011; 79604</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>122147; 128019</t>
+          <t>121883; 128019</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>185677; 197220</t>
+          <t>183644; 197221</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>97780; 106905</t>
+          <t>98021; 106896</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>93203; 100953</t>
+          <t>97951; 106204</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>191324; 202451</t>
+          <t>189934; 201733</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>313189; 326623</t>
+          <t>313033; 326581</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>172816; 187248</t>
+          <t>173432; 186461</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>164687; 176455</t>
+          <t>170359; 184049</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>66373</t>
+          <t>69399</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>108371</t>
+          <t>110856</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>174743</t>
+          <t>180255</t>
         </is>
       </c>
     </row>
@@ -2625,22 +2625,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>59549; 67578</t>
+          <t>58844; 67440</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>69575; 76522</t>
+          <t>69738; 76522</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>28766; 34645</t>
+          <t>28943; 34648</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>59817; 69450</t>
+          <t>64642; 72443</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -2650,37 +2650,37 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>86659; 96258</t>
+          <t>86201; 96258</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>35979; 43609</t>
+          <t>35408; 43484</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>101843; 111024</t>
+          <t>105332; 113461</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>145738; 153521</t>
+          <t>145818; 153526</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>160735; 171771</t>
+          <t>161444; 171774</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>67669; 77326</t>
+          <t>67979; 77356</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>167670; 179454</t>
+          <t>174160; 184693</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>70362</t>
+          <t>83563</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>83983</t>
+          <t>98105</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>154345</t>
+          <t>181667</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>68067; 74606</t>
+          <t>68356; 74606</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>70228; 80562</t>
+          <t>69147; 80562</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>84505; 94770</t>
+          <t>85293; 95331</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>57130; 75115</t>
+          <t>70094; 88884</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>95390; 102802</t>
+          <t>95363; 102813</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>94895; 103641</t>
+          <t>95640; 103677</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>102150; 117621</t>
+          <t>102432; 118177</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>77990; 87994</t>
+          <t>91174; 102412</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>167295; 176499</t>
+          <t>167155; 176450</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>170945; 182544</t>
+          <t>169127; 182240</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>194041; 211075</t>
+          <t>193776; 210788</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>142275; 161341</t>
+          <t>167634; 189001</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15844</t>
+          <t>17304</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>10092</t>
+          <t>11004</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>25936</t>
+          <t>28308</t>
         </is>
       </c>
     </row>
@@ -3041,32 +3041,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>30323; 34772</t>
+          <t>30237; 34772</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>29666; 36867</t>
+          <t>30657; 36867</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>20530; 26355</t>
+          <t>20545; 26355</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12689; 17208</t>
+          <t>13760; 18799</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>35660; 42041</t>
+          <t>35592; 42041</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>72255; 78914</t>
+          <t>72260; 78914</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -3081,22 +3081,22 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>68390; 76813</t>
+          <t>68305; 76813</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>106028; 114799</t>
+          <t>106106; 114764</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>49090; 54977</t>
+          <t>49276; 54977</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>22979; 27300</t>
+          <t>24902; 29803</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>67019</t>
+          <t>66431</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>73717</t>
+          <t>75073</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>140737</t>
+          <t>141504</t>
         </is>
       </c>
     </row>
@@ -3259,22 +3259,22 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>49144; 53724</t>
+          <t>48323; 53724</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>63412; 68335</t>
+          <t>62360; 67844</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>81394; 87395</t>
+          <t>81758; 87395</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>90896; 96148</t>
+          <t>91326; 96148</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -3284,27 +3284,27 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>70280; 75245</t>
+          <t>71260; 76726</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>140030; 145934</t>
+          <t>140476; 145934</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>155565; 160428</t>
+          <t>155603; 160428</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>123730; 129138</t>
+          <t>123364; 129138</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>136588; 142972</t>
+          <t>136899; 143748</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>143555</t>
+          <t>164474</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>395239</t>
+          <t>227808</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>538793</t>
+          <t>392282</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>90276; 103916</t>
+          <t>90804; 103681</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>139132; 144686</t>
+          <t>138362; 144686</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>62370; 72088</t>
+          <t>61977; 72021</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>131954; 150787</t>
+          <t>153092; 173747</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>148237; 162582</t>
+          <t>147984; 161957</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>171800; 182825</t>
+          <t>171619; 182756</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>98669; 114423</t>
+          <t>100763; 115256</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>358042; 420542</t>
+          <t>216993; 237427</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>244479; 263061</t>
+          <t>243987; 264082</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>314204; 325801</t>
+          <t>313959; 326397</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>167238; 185080</t>
+          <t>166641; 183962</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>501800; 574265</t>
+          <t>375033; 406188</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>80918</t>
+          <t>92419</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>99515</t>
+          <t>115721</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>180432</t>
+          <t>208140</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>87918; 97729</t>
+          <t>88088; 97726</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>60451; 67442</t>
+          <t>60204; 67459</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>76045; 90946</t>
+          <t>74399; 89920</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>75336; 85471</t>
+          <t>83959; 96915</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>141395; 150368</t>
+          <t>141732; 150554</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>89904; 102436</t>
+          <t>89452; 101823</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>114951; 131362</t>
+          <t>114124; 130889</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>92347; 104073</t>
+          <t>107319; 121980</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>234375; 246506</t>
+          <t>234100; 246781</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>154182; 168112</t>
+          <t>153650; 168028</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>196465; 218180</t>
+          <t>196342; 219007</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>171397; 187525</t>
+          <t>197483; 215349</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>617913</t>
+          <t>668936</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>976126</t>
+          <t>857103</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>1594039</t>
+          <t>1526040</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>521171; 541164</t>
+          <t>519926; 541582</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>674598; 692771</t>
+          <t>675363; 693539</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>496819; 521563</t>
+          <t>497676; 522076</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>599556; 632172</t>
+          <t>648060; 683339</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>785172; 805944</t>
+          <t>785811; 805989</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>934131; 956720</t>
+          <t>932772; 956899</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>676864; 708890</t>
+          <t>674988; 708250</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>951186; 1009867</t>
+          <t>839627; 871099</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1313868; 1343182</t>
+          <t>1314420; 1343697</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1615024; 1644064</t>
+          <t>1614688; 1644620</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1184632; 1223872</t>
+          <t>1186026; 1225070</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>1566789; 1637961</t>
+          <t>1499867; 1547622</t>
         </is>
       </c>
     </row>
